--- a/artfynd/A 15376-2023 artfynd.xlsx
+++ b/artfynd/A 15376-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15376-2023 artfynd.xlsx
+++ b/artfynd/A 15376-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>45042</v>
+        <v>30376</v>
       </c>
       <c r="B2" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -709,24 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NV om Trullefjäll kärrmark, Sm</t>
+          <t>NV Trullefjäll, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553565.05984595</v>
+        <v>553570</v>
       </c>
       <c r="R2" t="n">
-        <v>6245279.141903853</v>
+        <v>6245261</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-04-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>1990-04-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-04-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>1990-04-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,15 +760,127 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>45042</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58816</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100117</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Långbensgroda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana dalmatina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bonaparte, 1840</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NV om Trullefjäll kärrmark, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>553565</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6245279</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2008-04-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-04-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Helena Lager</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Helena Lager</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
